--- a/exim_aggregated.xlsx
+++ b/exim_aggregated.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G206"/>
+  <dimension ref="A1:H180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,30 +436,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>yyyymm</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>uom</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>GRADE/SPEC</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Sum_of_QTY</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Sum_of_TOTAL_VALUE</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Avg_PRICE</t>
         </is>
@@ -468,218 +473,253 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Advocure Pharmaceuticals</t>
+          <t>Brillant Pharmaceutical Ltd</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>202503</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nos</t>
+          <t>202505</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EP</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>12</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>6377.219999999999</v>
+        <v>3000</v>
       </c>
       <c r="G2" t="n">
-        <v>531.4299999999999</v>
+        <v>35201572</v>
+      </c>
+      <c r="H2" t="n">
+        <v>11733.86</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Advocure Pharmaceuticals</t>
+          <t>Brilliant Pharmaceutical Ltd</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>202503</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Nos</t>
+          <t>202501</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>6</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>2125.74</v>
+        <v>17954.6</v>
       </c>
       <c r="G3" t="n">
-        <v>354.29</v>
+        <v>215068360</v>
+      </c>
+      <c r="H3" t="n">
+        <v>11978.45</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Aldrich Chemical Co Llc</t>
+          <t>Brilliant Pharmaceutical Ltd</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>202502</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Nos</t>
+          <t>202501</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>4</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>27564.1</v>
+        <v>1000</v>
       </c>
       <c r="G4" t="n">
-        <v>6891.02</v>
+        <v>11871776</v>
+      </c>
+      <c r="H4" t="n">
+        <v>11871.78</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bio Rad Europe Gmbh</t>
+          <t>Brilliant Pharmaceutical Ltd</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>202501</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Nos</t>
+          <t>202507</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>52</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>23411.37</v>
+        <v>13500</v>
       </c>
       <c r="G5" t="n">
-        <v>450.22</v>
+        <v>160542774</v>
+      </c>
+      <c r="H5" t="n">
+        <v>11892.06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bio Rad Europe Gmbh</t>
+          <t>Brilliant Pharmaceutical Ltd</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>202503</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nos</t>
+          <t>202507</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>69</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>34932.02</v>
+        <v>9150</v>
       </c>
       <c r="G6" t="n">
-        <v>506.26</v>
+        <v>101647600</v>
+      </c>
+      <c r="H6" t="n">
+        <v>11109.03</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bio Rad Europe Gmbh</t>
+          <t>Brilliant Pharmaceutical Ltd</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>202512</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>202508</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>32</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>24688.15</v>
+        <v>13000</v>
       </c>
       <c r="G7" t="n">
-        <v>771.5</v>
+        <v>157867957</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12143.69</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Brillant Pharmaceutical Ltd</t>
+          <t>Brilliant Pharmaceutical Ltd</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>202505</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202508</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>IP</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>20000</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>35201572</v>
+        <v>11000</v>
       </c>
       <c r="G8" t="n">
-        <v>1760.08</v>
+        <v>119860164</v>
+      </c>
+      <c r="H8" t="n">
+        <v>10896.38</v>
       </c>
     </row>
     <row r="9">
@@ -690,27 +730,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>202501</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202509</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>IP</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>51675</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>EP</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>215607207</v>
+        <v>1000</v>
       </c>
       <c r="G9" t="n">
-        <v>4172.37</v>
+        <v>11494300</v>
+      </c>
+      <c r="H9" t="n">
+        <v>11494.3</v>
       </c>
     </row>
     <row r="10">
@@ -721,27 +766,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>202501</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202509</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>3025</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>11871776</v>
+        <v>4000</v>
       </c>
       <c r="G10" t="n">
-        <v>3924.55</v>
+        <v>49152198</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12288.05</v>
       </c>
     </row>
     <row r="11">
@@ -752,27 +802,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>202507</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202509</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>IP</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>1000</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>35715896</v>
+        <v>6850</v>
       </c>
       <c r="G11" t="n">
-        <v>35715.9</v>
+        <v>74309160</v>
+      </c>
+      <c r="H11" t="n">
+        <v>10848.05</v>
       </c>
     </row>
     <row r="12">
@@ -783,27 +838,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>202507</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202510</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>3000</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>EP</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>89823414</v>
+        <v>1950</v>
       </c>
       <c r="G12" t="n">
-        <v>29941.14</v>
+        <v>258073.67</v>
+      </c>
+      <c r="H12" t="n">
+        <v>132.35</v>
       </c>
     </row>
     <row r="13">
@@ -814,27 +874,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>202508</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202510</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>IP</t>
         </is>
       </c>
-      <c r="E13" t="n">
-        <v>8678.99</v>
-      </c>
       <c r="F13" t="n">
-        <v>157867957</v>
+        <v>1250</v>
       </c>
       <c r="G13" t="n">
-        <v>18189.67</v>
+        <v>171053.13</v>
+      </c>
+      <c r="H13" t="n">
+        <v>136.84</v>
       </c>
     </row>
     <row r="14">
@@ -845,27 +910,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>202508</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202510</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>8661.690000000001</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>119860164</v>
+        <v>12100</v>
       </c>
       <c r="G14" t="n">
-        <v>13837.97</v>
+        <v>1492659.28</v>
+      </c>
+      <c r="H14" t="n">
+        <v>123.36</v>
       </c>
     </row>
     <row r="15">
@@ -876,27 +946,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>202509</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202512</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>EP</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>4250</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
       </c>
       <c r="F15" t="n">
-        <v>11494300</v>
+        <v>2000</v>
       </c>
       <c r="G15" t="n">
-        <v>2704.54</v>
+        <v>25558814</v>
+      </c>
+      <c r="H15" t="n">
+        <v>12779.41</v>
       </c>
     </row>
     <row r="16">
@@ -907,27 +982,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>202509</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202601</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>IP</t>
         </is>
       </c>
-      <c r="E16" t="n">
-        <v>5350</v>
-      </c>
       <c r="F16" t="n">
-        <v>49152198</v>
+        <v>25000</v>
       </c>
       <c r="G16" t="n">
-        <v>9187.33</v>
+        <v>319007220</v>
+      </c>
+      <c r="H16" t="n">
+        <v>12760.29</v>
       </c>
     </row>
     <row r="17">
@@ -938,213 +1018,248 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>202509</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202602</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>14673.65</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
       </c>
       <c r="F17" t="n">
-        <v>74309160</v>
+        <v>2000</v>
       </c>
       <c r="G17" t="n">
-        <v>5064.12</v>
+        <v>25540704</v>
+      </c>
+      <c r="H17" t="n">
+        <v>12770.35</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Brilliant Pharmaceutical Ltd</t>
+          <t>Brilliant Pharmaceuticals Ltd</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>202510</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202502</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EP</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>700</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
       </c>
       <c r="F18" t="n">
-        <v>258073.67</v>
+        <v>11000</v>
       </c>
       <c r="G18" t="n">
-        <v>368.68</v>
+        <v>132862700</v>
+      </c>
+      <c r="H18" t="n">
+        <v>12078.43</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Brilliant Pharmaceutical Ltd</t>
+          <t>Brilliant Pharmaceuticals Ltd</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>202510</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202502</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>IP</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>757.3</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F19" t="n">
-        <v>171053.13</v>
+        <v>1000</v>
       </c>
       <c r="G19" t="n">
-        <v>225.87</v>
+        <v>12209991</v>
+      </c>
+      <c r="H19" t="n">
+        <v>12209.99</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Brilliant Pharmaceutical Ltd</t>
+          <t>Brilliant Pharmaceuticals Ltd</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>202510</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202503</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>1009.02</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
       </c>
       <c r="F20" t="n">
-        <v>1492659.28</v>
+        <v>6000</v>
       </c>
       <c r="G20" t="n">
-        <v>1479.32</v>
+        <v>72674426</v>
+      </c>
+      <c r="H20" t="n">
+        <v>12112.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Brilliant Pharmaceutical Ltd</t>
+          <t>Brilliant Pharmaceuticals Ltd</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>202512</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202503</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>IP</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>1494.5</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F21" t="n">
-        <v>25558814</v>
+        <v>6000</v>
       </c>
       <c r="G21" t="n">
-        <v>17101.92</v>
+        <v>71869577</v>
+      </c>
+      <c r="H21" t="n">
+        <v>11978.26</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Brilliant Pharmaceutical Ltd</t>
+          <t>Brilliant Pharmaceuticals Ltd</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>202601</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202504</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>IP</t>
         </is>
       </c>
-      <c r="E22" t="n">
-        <v>11975</v>
-      </c>
       <c r="F22" t="n">
-        <v>319007220</v>
+        <v>7000</v>
       </c>
       <c r="G22" t="n">
-        <v>26639.43</v>
+        <v>83432470</v>
+      </c>
+      <c r="H22" t="n">
+        <v>11918.92</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Brilliant Pharmaceutical Ltd</t>
+          <t>Brilliant Pharmaceuticals Ltd</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>202602</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202505</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>IP</t>
         </is>
       </c>
-      <c r="E23" t="n">
-        <v>2000</v>
-      </c>
       <c r="F23" t="n">
-        <v>25540704</v>
+        <v>13800</v>
       </c>
       <c r="G23" t="n">
-        <v>12770.35</v>
+        <v>162951220</v>
+      </c>
+      <c r="H23" t="n">
+        <v>11808.06</v>
       </c>
     </row>
     <row r="24">
@@ -1155,27 +1270,32 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>202502</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202505</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>IP</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>2000</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F24" t="n">
-        <v>35505285</v>
+        <v>3000</v>
       </c>
       <c r="G24" t="n">
-        <v>17752.64</v>
+        <v>35176586</v>
+      </c>
+      <c r="H24" t="n">
+        <v>11725.53</v>
       </c>
     </row>
     <row r="25">
@@ -1186,27 +1306,32 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>202503</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202506</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>IP</t>
         </is>
       </c>
-      <c r="E25" t="n">
-        <v>3551.76</v>
-      </c>
       <c r="F25" t="n">
-        <v>72674426</v>
+        <v>18000</v>
       </c>
       <c r="G25" t="n">
-        <v>20461.52</v>
+        <v>215032414</v>
+      </c>
+      <c r="H25" t="n">
+        <v>11946.25</v>
       </c>
     </row>
     <row r="26">
@@ -1217,27 +1342,32 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>202503</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202506</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>2000</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F26" t="n">
-        <v>71869577</v>
+        <v>10000</v>
       </c>
       <c r="G26" t="n">
-        <v>35934.79</v>
+        <v>107576200</v>
+      </c>
+      <c r="H26" t="n">
+        <v>10757.62</v>
       </c>
     </row>
     <row r="27">
@@ -1248,27 +1378,32 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>202504</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202511</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>IP</t>
         </is>
       </c>
-      <c r="E27" t="n">
-        <v>12220.4</v>
-      </c>
       <c r="F27" t="n">
-        <v>83432470</v>
+        <v>1750</v>
       </c>
       <c r="G27" t="n">
-        <v>6827.31</v>
+        <v>21286959</v>
+      </c>
+      <c r="H27" t="n">
+        <v>12163.98</v>
       </c>
     </row>
     <row r="28">
@@ -1279,27 +1414,32 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>202505</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202511</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>IP</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>19180</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F28" t="n">
-        <v>162951220</v>
+        <v>6850</v>
       </c>
       <c r="G28" t="n">
-        <v>8495.889999999999</v>
+        <v>74795148</v>
+      </c>
+      <c r="H28" t="n">
+        <v>10919</v>
       </c>
     </row>
     <row r="29">
@@ -1310,151 +1450,176 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>202505</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202502</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>1221.61</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
       </c>
       <c r="F29" t="n">
-        <v>35176586</v>
+        <v>3000</v>
       </c>
       <c r="G29" t="n">
-        <v>28795.27</v>
+        <v>35505285</v>
+      </c>
+      <c r="H29" t="n">
+        <v>11835.09</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Brilliant Pharmaceuticals Ltd</t>
+          <t>Cspc Ouyi Pharmaceutical Co Ltd</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>202506</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202501</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>IP</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>13300</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>EP</t>
+        </is>
       </c>
       <c r="F30" t="n">
-        <v>215032414</v>
+        <v>500</v>
       </c>
       <c r="G30" t="n">
-        <v>16167.85</v>
+        <v>6446250</v>
+      </c>
+      <c r="H30" t="n">
+        <v>12892.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Brilliant Pharmaceuticals Ltd</t>
+          <t>Cspc Ouyi Pharmaceutical Co Ltd</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>202506</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202501</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>4496.4</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
       </c>
       <c r="F31" t="n">
-        <v>107576200</v>
+        <v>4400</v>
       </c>
       <c r="G31" t="n">
-        <v>23924.96</v>
+        <v>53214988</v>
+      </c>
+      <c r="H31" t="n">
+        <v>12094.32</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Brilliant Pharmaceuticals Ltd</t>
+          <t>Cspc Ouyi Pharmaceutical Co Ltd</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>202511</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202501</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>IP</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>10000</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F32" t="n">
-        <v>21286959</v>
+        <v>3000</v>
       </c>
       <c r="G32" t="n">
-        <v>2128.7</v>
+        <v>35942140</v>
+      </c>
+      <c r="H32" t="n">
+        <v>11980.71</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Brilliant Pharmaceuticals Ltd</t>
+          <t>Cspc Ouyi Pharmaceutical Co Ltd</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>202511</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202502</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>10000</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
       </c>
       <c r="F33" t="n">
-        <v>74795148</v>
+        <v>5000</v>
       </c>
       <c r="G33" t="n">
-        <v>7479.51</v>
+        <v>60647999.5</v>
+      </c>
+      <c r="H33" t="n">
+        <v>12129.6</v>
       </c>
     </row>
     <row r="34">
@@ -1465,27 +1630,32 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>202501</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202502</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>EP</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>650</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F34" t="n">
-        <v>6446250</v>
+        <v>1800</v>
       </c>
       <c r="G34" t="n">
-        <v>9917.309999999999</v>
+        <v>25300080</v>
+      </c>
+      <c r="H34" t="n">
+        <v>14055.6</v>
       </c>
     </row>
     <row r="35">
@@ -1496,27 +1666,32 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>202501</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202503</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>IP</t>
         </is>
       </c>
-      <c r="E35" t="n">
-        <v>7500</v>
-      </c>
       <c r="F35" t="n">
-        <v>53214988</v>
+        <v>3000</v>
       </c>
       <c r="G35" t="n">
-        <v>7095.33</v>
+        <v>36575000</v>
+      </c>
+      <c r="H35" t="n">
+        <v>12191.67</v>
       </c>
     </row>
     <row r="36">
@@ -1527,27 +1702,32 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>202501</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202503</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>8174</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F36" t="n">
-        <v>35942140</v>
+        <v>5558</v>
       </c>
       <c r="G36" t="n">
-        <v>4397.13</v>
+        <v>77260228.5</v>
+      </c>
+      <c r="H36" t="n">
+        <v>13900.72</v>
       </c>
     </row>
     <row r="37">
@@ -1558,27 +1738,32 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>202502</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202505</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>IP</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>1000</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F37" t="n">
-        <v>24066000</v>
+        <v>2900</v>
       </c>
       <c r="G37" t="n">
-        <v>24066</v>
+        <v>37263375</v>
+      </c>
+      <c r="H37" t="n">
+        <v>12849.44</v>
       </c>
     </row>
     <row r="38">
@@ -1589,27 +1774,32 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>202503</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202506</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>IP</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>2875</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F38" t="n">
-        <v>36575000</v>
+        <v>2000</v>
       </c>
       <c r="G38" t="n">
-        <v>12721.74</v>
+        <v>25075106</v>
+      </c>
+      <c r="H38" t="n">
+        <v>12537.55</v>
       </c>
     </row>
     <row r="39">
@@ -1620,27 +1810,32 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>202503</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202507</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>4293.25</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F39" t="n">
-        <v>79231287.88</v>
+        <v>4960.41</v>
       </c>
       <c r="G39" t="n">
-        <v>18454.85</v>
+        <v>56676348.25</v>
+      </c>
+      <c r="H39" t="n">
+        <v>11425.74</v>
       </c>
     </row>
     <row r="40">
@@ -1651,27 +1846,32 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>202505</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202508</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>1003</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F40" t="n">
-        <v>37263375</v>
+        <v>2500</v>
       </c>
       <c r="G40" t="n">
-        <v>37151.92</v>
+        <v>29600900</v>
+      </c>
+      <c r="H40" t="n">
+        <v>11840.36</v>
       </c>
     </row>
     <row r="41">
@@ -1682,27 +1882,32 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>202506</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202509</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>3638</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F41" t="n">
-        <v>25075106</v>
+        <v>8891.4</v>
       </c>
       <c r="G41" t="n">
-        <v>6892.55</v>
+        <v>122640217</v>
+      </c>
+      <c r="H41" t="n">
+        <v>13793.13</v>
       </c>
     </row>
     <row r="42">
@@ -1713,27 +1918,32 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>202507</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202510</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>1000</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F42" t="n">
-        <v>21538796</v>
+        <v>1350</v>
       </c>
       <c r="G42" t="n">
-        <v>21538.8</v>
+        <v>179550</v>
+      </c>
+      <c r="H42" t="n">
+        <v>133</v>
       </c>
     </row>
     <row r="43">
@@ -1744,27 +1954,32 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>202508</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202511</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>3669.04</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F43" t="n">
-        <v>29600900</v>
+        <v>2000</v>
       </c>
       <c r="G43" t="n">
-        <v>8067.75</v>
+        <v>24164999.5</v>
+      </c>
+      <c r="H43" t="n">
+        <v>12082.5</v>
       </c>
     </row>
     <row r="44">
@@ -1775,27 +1990,32 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>202509</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202512</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>11700</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F44" t="n">
-        <v>124174425.46</v>
+        <v>1000</v>
       </c>
       <c r="G44" t="n">
-        <v>10613.2</v>
+        <v>12325500</v>
+      </c>
+      <c r="H44" t="n">
+        <v>12325.5</v>
       </c>
     </row>
     <row r="45">
@@ -1806,430 +2026,500 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>202510</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202601</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>260</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F45" t="n">
-        <v>179550</v>
+        <v>1494.5</v>
       </c>
       <c r="G45" t="n">
-        <v>690.58</v>
+        <v>20713795</v>
+      </c>
+      <c r="H45" t="n">
+        <v>13860.02</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cspc Ouyi Pharmaceutical Co Ltd</t>
+          <t>Hangzhou Dawn Ray Pharmaceutical Co Ltd</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>202511</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202502</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>10250</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F46" t="n">
-        <v>24164999.5</v>
+        <v>500</v>
       </c>
       <c r="G46" t="n">
-        <v>2357.56</v>
+        <v>6188000</v>
+      </c>
+      <c r="H46" t="n">
+        <v>12376</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Cspc Ouyi Pharmaceutical Co Ltd</t>
+          <t>Hangzhou Dawn Ray Pharmaceutical Co Ltd</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>202512</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202503</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>5500</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F47" t="n">
-        <v>12325500</v>
+        <v>2131.93</v>
       </c>
       <c r="G47" t="n">
-        <v>2241</v>
+        <v>25876646</v>
+      </c>
+      <c r="H47" t="n">
+        <v>12137.66</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cspc Ouyi Pharmaceutical Co Ltd</t>
+          <t>Hangzhou Dawn Ray Pharmaceutical Co Ltd</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>202601</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202504</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>2343.91</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F48" t="n">
-        <v>25124359.63</v>
+        <v>1250</v>
       </c>
       <c r="G48" t="n">
-        <v>10719</v>
+        <v>14719875</v>
+      </c>
+      <c r="H48" t="n">
+        <v>11775.9</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Edqm Council Of Europe</t>
+          <t>Hangzhou Dawn Ray Pharmaceutical Co Ltd</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>202505</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Nos</t>
+          <t>202506</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>6</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F49" t="n">
-        <v>47701.95</v>
+        <v>801.76</v>
       </c>
       <c r="G49" t="n">
-        <v>7950.32</v>
+        <v>9514807</v>
+      </c>
+      <c r="H49" t="n">
+        <v>11867.4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>European Directorate For The Quality Of Medicines</t>
+          <t>Hangzhou Insure Chemical Co Ltd</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>202509</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Nos</t>
+          <t>202507</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>4</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F50" t="n">
-        <v>34092.54</v>
+        <v>260</v>
       </c>
       <c r="G50" t="n">
-        <v>8523.139999999999</v>
+        <v>3148236</v>
+      </c>
+      <c r="H50" t="n">
+        <v>12108.6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>European Directorate For The Quality Of Medicines</t>
+          <t>Hebei Guolong Pharmaceutical Co Ltd</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>202511</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Nos</t>
+          <t>202501</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>8</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F51" t="n">
-        <v>67971</v>
+        <v>19000</v>
       </c>
       <c r="G51" t="n">
-        <v>8496.379999999999</v>
+        <v>224324720.25</v>
+      </c>
+      <c r="H51" t="n">
+        <v>11806.56</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>European Directorate For The Quality Of Medicines And Healthcare</t>
+          <t>Hebei Guolong Pharmaceutical Co Ltd</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>202601</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Nos</t>
+          <t>202502</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>2</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F52" t="n">
-        <v>19812.54</v>
+        <v>7000</v>
       </c>
       <c r="G52" t="n">
-        <v>9906.27</v>
+        <v>84156800</v>
+      </c>
+      <c r="H52" t="n">
+        <v>12022.4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Fresenius Kabi Llc</t>
+          <t>Hebei Guolong Pharmaceutical Co Ltd</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>202504</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Gms</t>
+          <t>202503</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>10</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F53" t="n">
-        <v>259.2</v>
+        <v>3000</v>
       </c>
       <c r="G53" t="n">
-        <v>25.92</v>
+        <v>35923862</v>
+      </c>
+      <c r="H53" t="n">
+        <v>11974.62</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Gm Pharmaceuticals</t>
+          <t>Hebei Guolong Pharmaceutical Co Ltd</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>202501</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202505</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>EP</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>2500</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F54" t="n">
-        <v>24707.66</v>
+        <v>4000</v>
       </c>
       <c r="G54" t="n">
-        <v>9.880000000000001</v>
+        <v>47855461.5</v>
+      </c>
+      <c r="H54" t="n">
+        <v>11963.87</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Hangzhou Dawn Ray Pharmaceutical Co Ltd</t>
+          <t>Hebei Guolong Pharmaceutical Co Ltd</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>202503</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202506</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>6678.2</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F55" t="n">
-        <v>27558692.38</v>
+        <v>4000</v>
       </c>
       <c r="G55" t="n">
-        <v>4126.66</v>
+        <v>48713048</v>
+      </c>
+      <c r="H55" t="n">
+        <v>12178.26</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Hangzhou Dawn Ray Pharmaceutical Co Ltd</t>
+          <t>Hebei Guolong Pharmaceutical Co Ltd</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>202504</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202507</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>9300</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F56" t="n">
-        <v>14719875</v>
+        <v>11000</v>
       </c>
       <c r="G56" t="n">
-        <v>1582.78</v>
+        <v>129489449</v>
+      </c>
+      <c r="H56" t="n">
+        <v>11771.77</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Hangzhou Dawn Ray Pharmaceutical Co Ltd</t>
+          <t>Hebei Guolong Pharmaceutical Co Ltd</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>202506</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202508</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>2242.56</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F57" t="n">
-        <v>11867400.5</v>
+        <v>2000</v>
       </c>
       <c r="G57" t="n">
-        <v>5291.9</v>
+        <v>24808000</v>
+      </c>
+      <c r="H57" t="n">
+        <v>12404</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Hangzhou Dawn Ray Pharmaceutical Co Ltd</t>
+          <t>Hebei Guolong Pharmaceutical Co Ltd</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>202512</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202509</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
         <v>1000</v>
       </c>
-      <c r="F58" t="n">
-        <v>528050</v>
-      </c>
       <c r="G58" t="n">
-        <v>528.05</v>
+        <v>12446053</v>
+      </c>
+      <c r="H58" t="n">
+        <v>12446.05</v>
       </c>
     </row>
     <row r="59">
@@ -2240,27 +2530,32 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>202501</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202511</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>42473.01</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F59" t="n">
-        <v>224324720.25</v>
+        <v>12000</v>
       </c>
       <c r="G59" t="n">
-        <v>5281.58</v>
+        <v>144733541</v>
+      </c>
+      <c r="H59" t="n">
+        <v>12061.13</v>
       </c>
     </row>
     <row r="60">
@@ -2271,461 +2566,536 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>202503</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202512</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>2850</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F60" t="n">
-        <v>35923862</v>
+        <v>3000</v>
       </c>
       <c r="G60" t="n">
-        <v>12604.86</v>
+        <v>38101050</v>
+      </c>
+      <c r="H60" t="n">
+        <v>12700.35</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Hebei Guolong Pharmaceutical Co Ltd</t>
+          <t>Hebei Guolong Pharmaceuticals Co Ltd</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>202505</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202501</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>4131.93</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F61" t="n">
-        <v>47855461.5</v>
+        <v>2000</v>
       </c>
       <c r="G61" t="n">
-        <v>11581.87</v>
+        <v>23555200</v>
+      </c>
+      <c r="H61" t="n">
+        <v>11777.6</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Hebei Guolong Pharmaceutical Co Ltd</t>
+          <t>Hebei Guolonh Pharmaceutical Co Ltd</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>202506</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202509</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>5829.9</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F62" t="n">
-        <v>48713048</v>
+        <v>4000</v>
       </c>
       <c r="G62" t="n">
-        <v>8355.73</v>
+        <v>49224000</v>
+      </c>
+      <c r="H62" t="n">
+        <v>12306</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Hebei Guolong Pharmaceutical Co Ltd</t>
+          <t>Hebei Sunco Biotech Co Ltd</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>202508</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202504</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>10000</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
       </c>
       <c r="F63" t="n">
-        <v>24808000</v>
+        <v>1000</v>
       </c>
       <c r="G63" t="n">
-        <v>2480.8</v>
+        <v>11846510</v>
+      </c>
+      <c r="H63" t="n">
+        <v>11846.51</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Hebei Guolong Pharmaceutical Co Ltd</t>
+          <t>Hebei Sunco Biotech Co Ltd</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>202509</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202505</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>3000</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
       </c>
       <c r="F64" t="n">
-        <v>12446053</v>
+        <v>816</v>
       </c>
       <c r="G64" t="n">
-        <v>4148.68</v>
+        <v>9571135</v>
+      </c>
+      <c r="H64" t="n">
+        <v>11729.33</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Hebei Guolong Pharmaceutical Co Ltd</t>
+          <t>Hebei Sunco Biotech Co Ltd</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>202511</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202509</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>25275</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
       </c>
       <c r="F65" t="n">
-        <v>144733541</v>
+        <v>1000</v>
       </c>
       <c r="G65" t="n">
-        <v>5726.35</v>
+        <v>12200914</v>
+      </c>
+      <c r="H65" t="n">
+        <v>12200.91</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Hebei Guolong Pharmaceutical Co Ltd</t>
+          <t>Heilongjiang Lianshun Biotech C</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>202512</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202509</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>3367.44</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F66" t="n">
-        <v>38101050</v>
+        <v>9400</v>
       </c>
       <c r="G66" t="n">
-        <v>11314.54</v>
+        <v>102758012</v>
+      </c>
+      <c r="H66" t="n">
+        <v>10931.7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Hebei Guolong Pharmaceuticals Co Ltd</t>
+          <t>Heilongjiang Lianshun Biotech Co</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>202501</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202502</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>2000</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F67" t="n">
-        <v>23555200</v>
+        <v>11325</v>
       </c>
       <c r="G67" t="n">
-        <v>11777.6</v>
+        <v>123705558</v>
+      </c>
+      <c r="H67" t="n">
+        <v>10923.23</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Hebei Guolonh Pharmaceutical Co Ltd</t>
+          <t>Heilongjiang Lianshun Biotech Co</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>202509</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202503</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>16250</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F68" t="n">
-        <v>49224000</v>
+        <v>19200</v>
       </c>
       <c r="G68" t="n">
-        <v>3029.17</v>
+        <v>208187296</v>
+      </c>
+      <c r="H68" t="n">
+        <v>10843.09</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Hebei Sunco Biotech Co Ltd</t>
+          <t>Heilongjiang Lianshun Biotech Co</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
           <t>202504</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>IP</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>5000</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F69" t="n">
-        <v>11846510</v>
+        <v>15000</v>
       </c>
       <c r="G69" t="n">
-        <v>2369.3</v>
+        <v>160247251</v>
+      </c>
+      <c r="H69" t="n">
+        <v>10683.15</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Hebei Sunco Biotech Co Ltd</t>
+          <t>Heilongjiang Lianshun Biotech Co Ltd</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>202505</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202501</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>IP</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>400</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F70" t="n">
-        <v>11729332</v>
+        <v>29000</v>
       </c>
       <c r="G70" t="n">
-        <v>29323.33</v>
+        <v>313158237</v>
+      </c>
+      <c r="H70" t="n">
+        <v>10798.56</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Hebei Sunco Biotech Co Ltd</t>
+          <t>Heilongjiang Lianshun Biotech Co Ltd</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>202509</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202502</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>IP</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>2000</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F71" t="n">
-        <v>12200914</v>
+        <v>5375</v>
       </c>
       <c r="G71" t="n">
-        <v>6100.46</v>
+        <v>59079512</v>
+      </c>
+      <c r="H71" t="n">
+        <v>10991.54</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Heilongjiang Lianshun Biotech C</t>
+          <t>Heilongjiang Lianshun Biotech Co Ltd</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>202509</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202503</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>3445.5</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F72" t="n">
-        <v>102758012</v>
+        <v>19000</v>
       </c>
       <c r="G72" t="n">
-        <v>29823.83</v>
+        <v>207104420</v>
+      </c>
+      <c r="H72" t="n">
+        <v>10900.23</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Heilongjiang Lianshun Biotech Co</t>
+          <t>Heilongjiang Lianshun Biotech Co Ltd</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>202503</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202504</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>2000</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F73" t="n">
-        <v>208187296</v>
+        <v>16125</v>
       </c>
       <c r="G73" t="n">
-        <v>104093.65</v>
+        <v>175925001</v>
+      </c>
+      <c r="H73" t="n">
+        <v>10910.08</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Heilongjiang Lianshun Biotech Co</t>
+          <t>Heilongjiang Lianshun Biotech Co Ltd</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>202504</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202505</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>18407</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F74" t="n">
-        <v>160247251</v>
+        <v>31300</v>
       </c>
       <c r="G74" t="n">
-        <v>8705.780000000001</v>
+        <v>334407543.5</v>
+      </c>
+      <c r="H74" t="n">
+        <v>10683.95</v>
       </c>
     </row>
     <row r="75">
@@ -2736,27 +3106,32 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>202501</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202506</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>18641.4</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F75" t="n">
-        <v>313158237</v>
+        <v>22000</v>
       </c>
       <c r="G75" t="n">
-        <v>16799.07</v>
+        <v>238021480</v>
+      </c>
+      <c r="H75" t="n">
+        <v>10819.16</v>
       </c>
     </row>
     <row r="76">
@@ -2767,27 +3142,32 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>202503</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202507</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>3816</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F76" t="n">
-        <v>207104420</v>
+        <v>40725</v>
       </c>
       <c r="G76" t="n">
-        <v>54272.65</v>
+        <v>434692806.25</v>
+      </c>
+      <c r="H76" t="n">
+        <v>10673.86</v>
       </c>
     </row>
     <row r="77">
@@ -2798,27 +3178,32 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>202504</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202509</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>11878</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F77" t="n">
-        <v>175925001</v>
+        <v>25950</v>
       </c>
       <c r="G77" t="n">
-        <v>14811</v>
+        <v>279663829</v>
+      </c>
+      <c r="H77" t="n">
+        <v>10777.03</v>
       </c>
     </row>
     <row r="78">
@@ -2829,27 +3214,32 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>202505</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202510</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>13804.59</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F78" t="n">
-        <v>334407543.5</v>
+        <v>30925</v>
       </c>
       <c r="G78" t="n">
-        <v>24224.37</v>
+        <v>3803775</v>
+      </c>
+      <c r="H78" t="n">
+        <v>123</v>
       </c>
     </row>
     <row r="79">
@@ -2860,27 +3250,32 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>202506</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202511</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
-        <v>7448.690000000001</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F79" t="n">
-        <v>238021480</v>
+        <v>39100</v>
       </c>
       <c r="G79" t="n">
-        <v>31954.81</v>
+        <v>429413053.5</v>
+      </c>
+      <c r="H79" t="n">
+        <v>10982.43</v>
       </c>
     </row>
     <row r="80">
@@ -2891,27 +3286,32 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>202507</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202512</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>1000</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F80" t="n">
-        <v>38961660</v>
+        <v>32225</v>
       </c>
       <c r="G80" t="n">
-        <v>38961.66</v>
+        <v>358028904</v>
+      </c>
+      <c r="H80" t="n">
+        <v>11110.28</v>
       </c>
     </row>
     <row r="81">
@@ -2922,740 +3322,860 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>202509</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202601</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>16776.52</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F81" t="n">
-        <v>279663829</v>
+        <v>16800</v>
       </c>
       <c r="G81" t="n">
-        <v>16669.95</v>
+        <v>188232657</v>
+      </c>
+      <c r="H81" t="n">
+        <v>11204.32</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Heilongjiang Lianshun Biotech Co Ltd</t>
+          <t>Hong Kong  Osiris International Co Ltd</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>202510</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202501</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>9754.799999999999</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F82" t="n">
-        <v>3803775</v>
+        <v>5000</v>
       </c>
       <c r="G82" t="n">
-        <v>389.94</v>
+        <v>54242052</v>
+      </c>
+      <c r="H82" t="n">
+        <v>10848.41</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Heilongjiang Lianshun Biotech Co Ltd</t>
+          <t>Hong Kong Osiris International Co Ltd</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>202511</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202503</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E83" t="n">
-        <v>50550</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F83" t="n">
-        <v>429413053.5</v>
+        <v>5550</v>
       </c>
       <c r="G83" t="n">
-        <v>8494.82</v>
+        <v>60718207.75</v>
+      </c>
+      <c r="H83" t="n">
+        <v>10940.22</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Heilongjiang Lianshun Biotech Co Ltd</t>
+          <t>Hong Kong Osiris International Co Ltd</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>202512</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202504</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E84" t="n">
-        <v>8607</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F84" t="n">
-        <v>358028904</v>
+        <v>1000</v>
       </c>
       <c r="G84" t="n">
-        <v>41597.41</v>
+        <v>10902604</v>
+      </c>
+      <c r="H84" t="n">
+        <v>10902.6</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Heilongjiang Lianshun Biotech Co Ltd</t>
+          <t>Hong Kong Osiris International Co Ltd</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>202601</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202505</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
-        <v>3470.84</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F85" t="n">
-        <v>188232657</v>
+        <v>7075</v>
       </c>
       <c r="G85" t="n">
-        <v>54232.59</v>
+        <v>75303316</v>
+      </c>
+      <c r="H85" t="n">
+        <v>10643.58</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Hong Kong  Osiris International Co Ltd</t>
+          <t>Hong Kong Osiris International Co Ltd</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>202501</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202506</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E86" t="n">
-        <v>6458</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F86" t="n">
-        <v>54242052</v>
+        <v>6375</v>
       </c>
       <c r="G86" t="n">
-        <v>8399.200000000001</v>
+        <v>68564468</v>
+      </c>
+      <c r="H86" t="n">
+        <v>10755.21</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Hong Kong Osiris International Co Ltd</t>
+          <t>Hong Kong Xinsheng Medical Technolo</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>202503</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202501</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E87" t="n">
-        <v>2351.72</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F87" t="n">
-        <v>60718207.75</v>
+        <v>4000</v>
       </c>
       <c r="G87" t="n">
-        <v>25818.64</v>
+        <v>47057820</v>
+      </c>
+      <c r="H87" t="n">
+        <v>11764.45</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Hong Kong Osiris International Co Ltd</t>
+          <t>Hong Kong Xinsheng Medical Technolo</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>202504</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202503</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E88" t="n">
-        <v>4500</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F88" t="n">
-        <v>10902604</v>
+        <v>4000</v>
       </c>
       <c r="G88" t="n">
-        <v>2422.8</v>
+        <v>47428552</v>
+      </c>
+      <c r="H88" t="n">
+        <v>11857.14</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Hong Kong Osiris International Co Ltd</t>
+          <t>Hong Kong Xinsheng Medical Technology</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>202505</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202501</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E89" t="n">
-        <v>13845.23</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F89" t="n">
-        <v>75303316</v>
+        <v>7500</v>
       </c>
       <c r="G89" t="n">
-        <v>5438.94</v>
+        <v>88332000</v>
+      </c>
+      <c r="H89" t="n">
+        <v>11777.6</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Hong Kong Osiris International Co Ltd</t>
+          <t>Hong Kong Xinsheng Medical Technology Co Ltd</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>202506</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202510</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E90" t="n">
-        <v>4500</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F90" t="n">
-        <v>68564468</v>
+        <v>4000</v>
       </c>
       <c r="G90" t="n">
-        <v>15236.55</v>
+        <v>526000</v>
+      </c>
+      <c r="H90" t="n">
+        <v>131.5</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Hong Kong Xinsheng Medical Technolo</t>
+          <t>Hong Kong Xinsheng Medical Technology Co Ltd</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>202501</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202511</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E91" t="n">
-        <v>3125</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F91" t="n">
-        <v>47057820</v>
+        <v>10350</v>
       </c>
       <c r="G91" t="n">
-        <v>15058.5</v>
+        <v>115455624</v>
+      </c>
+      <c r="H91" t="n">
+        <v>11155.13</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Hong Kong Xinsheng Medical Technolo</t>
+          <t>Hong Kong Xinsheng Medical Technology Co Ltd</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>202503</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202602</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E92" t="n">
-        <v>768.4400000000001</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F92" t="n">
-        <v>47428552</v>
+        <v>5000</v>
       </c>
       <c r="G92" t="n">
-        <v>61720.57</v>
+        <v>57115558</v>
+      </c>
+      <c r="H92" t="n">
+        <v>11423.11</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Hong Kong Xinsheng Medical Technology</t>
+          <t>Hong Kong Xinsheng Medical Technology Co Ltd</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>202501</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202502</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E93" t="n">
-        <v>12000</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F93" t="n">
-        <v>88332000</v>
+        <v>1750</v>
       </c>
       <c r="G93" t="n">
-        <v>7361</v>
+        <v>21194820</v>
+      </c>
+      <c r="H93" t="n">
+        <v>12111.33</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Hong Kong Xinsheng Medical Technology Co Ltd</t>
+          <t>Hongkong Osiris International Co Ltd</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>202510</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202507</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E94" t="n">
-        <v>901.35</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F94" t="n">
-        <v>526000</v>
+        <v>10000</v>
       </c>
       <c r="G94" t="n">
-        <v>583.5700000000001</v>
+        <v>106460376</v>
+      </c>
+      <c r="H94" t="n">
+        <v>10646.04</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Hong Kong Xinsheng Medical Technology Co Ltd</t>
+          <t>Hongkong Osiris International Co Ltd</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>202511</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202602</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E95" t="n">
-        <v>25000</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F95" t="n">
-        <v>115455624</v>
+        <v>14625</v>
       </c>
       <c r="G95" t="n">
-        <v>4618.22</v>
+        <v>165710792</v>
+      </c>
+      <c r="H95" t="n">
+        <v>11330.65</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Hong Kong Xinsheng Medical Technology Co Ltd</t>
+          <t>Huei Ho International Co Ltd</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>202602</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202505</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E96" t="n">
-        <v>2000</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F96" t="n">
-        <v>57115558</v>
+        <v>10000</v>
       </c>
       <c r="G96" t="n">
-        <v>28557.78</v>
+        <v>106755720</v>
+      </c>
+      <c r="H96" t="n">
+        <v>10675.57</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Hongkong Osiris International Co Ltd</t>
+          <t>Huei Ho International Co Ltd</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>202507</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202601</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E97" t="n">
-        <v>1000</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F97" t="n">
-        <v>53409016</v>
+        <v>10500</v>
       </c>
       <c r="G97" t="n">
-        <v>53409.02</v>
+        <v>116376644</v>
+      </c>
+      <c r="H97" t="n">
+        <v>11083.49</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Hongkong Osiris International Co Ltd</t>
+          <t>Jiangsu Guotai Goumian Trading Co Ltd</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>202602</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202503</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E98" t="n">
-        <v>3000</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F98" t="n">
-        <v>165710792</v>
+        <v>1600</v>
       </c>
       <c r="G98" t="n">
-        <v>55236.93</v>
+        <v>18964800</v>
+      </c>
+      <c r="H98" t="n">
+        <v>11853</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Huei Ho International Co Ltd</t>
+          <t>Longchem Internationaltrading Co Ltd</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>202505</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202503</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E99" t="n">
-        <v>4000</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
       </c>
       <c r="F99" t="n">
-        <v>106755720</v>
+        <v>5125</v>
       </c>
       <c r="G99" t="n">
-        <v>26688.93</v>
+        <v>62196102</v>
+      </c>
+      <c r="H99" t="n">
+        <v>12135.82</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Huei Ho International Co Ltd</t>
+          <t>Longchem Internationaltrading Co Ltd</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>202601</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202504</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E100" t="n">
-        <v>4860</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
       </c>
       <c r="F100" t="n">
-        <v>116376644</v>
+        <v>14825</v>
       </c>
       <c r="G100" t="n">
-        <v>23945.81</v>
+        <v>178141816</v>
+      </c>
+      <c r="H100" t="n">
+        <v>12016.31</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Jiangsu Guotai Goumian Trading Co Ltd</t>
+          <t>Mdnf</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>202503</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202505</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E101" t="n">
-        <v>2050</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F101" t="n">
-        <v>18964800</v>
+        <v>3546.04</v>
       </c>
       <c r="G101" t="n">
-        <v>9251.120000000001</v>
+        <v>42892791.25</v>
+      </c>
+      <c r="H101" t="n">
+        <v>12095.97</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Longchem Internationaltrading Co Ltd</t>
+          <t>Ningxia Taiyicin Biotech Co Ltd</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>202503</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202501</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>IP</t>
-        </is>
-      </c>
-      <c r="E102" t="n">
-        <v>3000</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F102" t="n">
-        <v>62196102</v>
+        <v>5500</v>
       </c>
       <c r="G102" t="n">
-        <v>20732.03</v>
+        <v>60146934</v>
+      </c>
+      <c r="H102" t="n">
+        <v>10935.81</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Longchem Internationaltrading Co Ltd</t>
+          <t>Ningxia Taiyicin Biotech Co Ltd</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>202504</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202502</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>IP</t>
-        </is>
-      </c>
-      <c r="E103" t="n">
-        <v>13907.05</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F103" t="n">
-        <v>178141816</v>
+        <v>8750</v>
       </c>
       <c r="G103" t="n">
-        <v>12809.46</v>
+        <v>102117492</v>
+      </c>
+      <c r="H103" t="n">
+        <v>11670.57</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Mdnf</t>
+          <t>Ningxia Taiyicin Biotech Co Ltd</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>202505</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202503</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E104" t="n">
-        <v>38389.61</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F104" t="n">
-        <v>48384000.25</v>
+        <v>7750</v>
       </c>
       <c r="G104" t="n">
-        <v>1260.34</v>
+        <v>91751156</v>
+      </c>
+      <c r="H104" t="n">
+        <v>11838.86</v>
       </c>
     </row>
     <row r="105">
@@ -3666,27 +4186,32 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>202501</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202504</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E105" t="n">
-        <v>7475</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F105" t="n">
-        <v>61043244</v>
+        <v>10000</v>
       </c>
       <c r="G105" t="n">
-        <v>8166.32</v>
+        <v>110277462</v>
+      </c>
+      <c r="H105" t="n">
+        <v>11027.75</v>
       </c>
     </row>
     <row r="106">
@@ -3697,27 +4222,32 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>202502</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202505</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E106" t="n">
-        <v>3000</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F106" t="n">
-        <v>102117492</v>
+        <v>6000</v>
       </c>
       <c r="G106" t="n">
-        <v>34039.16</v>
+        <v>64370506</v>
+      </c>
+      <c r="H106" t="n">
+        <v>10728.42</v>
       </c>
     </row>
     <row r="107">
@@ -3728,27 +4258,32 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>202503</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202506</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E107" t="n">
-        <v>5025</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F107" t="n">
-        <v>91751156</v>
+        <v>4500</v>
       </c>
       <c r="G107" t="n">
-        <v>18258.94</v>
+        <v>48583296</v>
+      </c>
+      <c r="H107" t="n">
+        <v>10796.29</v>
       </c>
     </row>
     <row r="108">
@@ -3759,27 +4294,32 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>202504</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202507</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E108" t="n">
-        <v>7475</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F108" t="n">
-        <v>110277462</v>
+        <v>1000</v>
       </c>
       <c r="G108" t="n">
-        <v>14752.84</v>
+        <v>10693845</v>
+      </c>
+      <c r="H108" t="n">
+        <v>10693.84</v>
       </c>
     </row>
     <row r="109">
@@ -3790,27 +4330,32 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>202505</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202508</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E109" t="n">
-        <v>12600</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F109" t="n">
-        <v>64370506</v>
+        <v>2000</v>
       </c>
       <c r="G109" t="n">
-        <v>5108.77</v>
+        <v>23603040</v>
+      </c>
+      <c r="H109" t="n">
+        <v>11801.52</v>
       </c>
     </row>
     <row r="110">
@@ -3821,27 +4366,32 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>202506</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202509</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E110" t="n">
-        <v>12000</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F110" t="n">
-        <v>48583296</v>
+        <v>3784</v>
       </c>
       <c r="G110" t="n">
-        <v>4048.61</v>
+        <v>42256480</v>
+      </c>
+      <c r="H110" t="n">
+        <v>11167.15</v>
       </c>
     </row>
     <row r="111">
@@ -3852,27 +4402,32 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>202507</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202510</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E111" t="n">
-        <v>1000</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F111" t="n">
-        <v>10693845</v>
+        <v>8000</v>
       </c>
       <c r="G111" t="n">
-        <v>10693.84</v>
+        <v>1003068.91</v>
+      </c>
+      <c r="H111" t="n">
+        <v>125.38</v>
       </c>
     </row>
     <row r="112">
@@ -3883,27 +4438,32 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>202508</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202511</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E112" t="n">
-        <v>950</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F112" t="n">
-        <v>23603040</v>
+        <v>6000</v>
       </c>
       <c r="G112" t="n">
-        <v>24845.31</v>
+        <v>65246884</v>
+      </c>
+      <c r="H112" t="n">
+        <v>10874.48</v>
       </c>
     </row>
     <row r="113">
@@ -3914,27 +4474,32 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>202509</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202512</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E113" t="n">
-        <v>11375</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F113" t="n">
-        <v>42268510.76</v>
+        <v>27750</v>
       </c>
       <c r="G113" t="n">
-        <v>3715.91</v>
+        <v>311538844</v>
+      </c>
+      <c r="H113" t="n">
+        <v>11226.63</v>
       </c>
     </row>
     <row r="114">
@@ -3945,27 +4510,32 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>202510</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202601</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E114" t="n">
-        <v>499.83</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F114" t="n">
-        <v>1003068.91</v>
+        <v>14961.8</v>
       </c>
       <c r="G114" t="n">
-        <v>2006.82</v>
+        <v>167915526</v>
+      </c>
+      <c r="H114" t="n">
+        <v>11222.95</v>
       </c>
     </row>
     <row r="115">
@@ -3976,2848 +4546,2372 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>202511</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202602</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E115" t="n">
-        <v>10000</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F115" t="n">
-        <v>65246884</v>
+        <v>23653.23</v>
       </c>
       <c r="G115" t="n">
-        <v>6524.69</v>
+        <v>265742884</v>
+      </c>
+      <c r="H115" t="n">
+        <v>11234.95</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Ningxia Taiyicin Biotech Co Ltd</t>
+          <t>Shanxi Yuncida Import And Export Co Ltd</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>202512</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202502</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E116" t="n">
-        <v>3695.01</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
       </c>
       <c r="F116" t="n">
-        <v>311538844</v>
+        <v>2000</v>
       </c>
       <c r="G116" t="n">
-        <v>84313.39999999999</v>
+        <v>24243324</v>
+      </c>
+      <c r="H116" t="n">
+        <v>12121.66</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Ningxia Taiyicin Biotech Co Ltd</t>
+          <t>Sinobright Pharmaceutical Indusrtries Ltd</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>202601</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202502</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E117" t="n">
-        <v>13365.21</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
       </c>
       <c r="F117" t="n">
-        <v>169197583.38</v>
+        <v>4250</v>
       </c>
       <c r="G117" t="n">
-        <v>12659.55</v>
+        <v>51246976</v>
+      </c>
+      <c r="H117" t="n">
+        <v>12058.11</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Ningxia Taiyicin Biotech Co Ltd</t>
+          <t>Sinobright Pharmaceutical Indusrtries Ltd</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>202602</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202503</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E118" t="n">
-        <v>19821</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
       </c>
       <c r="F118" t="n">
-        <v>267954380.5</v>
+        <v>2250</v>
       </c>
       <c r="G118" t="n">
-        <v>13518.71</v>
+        <v>27048938</v>
+      </c>
+      <c r="H118" t="n">
+        <v>12021.75</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Pharmacopeia Convention Inc</t>
+          <t>Sinobright Pharmaceutical Indusrtries Ltd</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>202504</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Nos</t>
+          <t>202503</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E119" t="n">
-        <v>1</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F119" t="n">
-        <v>24783.51</v>
+        <v>4500</v>
       </c>
       <c r="G119" t="n">
-        <v>24783.51</v>
+        <v>55890774</v>
+      </c>
+      <c r="H119" t="n">
+        <v>12420.17</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Pharmacopeia Convention Inc</t>
+          <t>Sinobright Pharmaceutical Indusrtries Ltd</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>202511</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Nos</t>
+          <t>202504</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E120" t="n">
-        <v>1</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
       </c>
       <c r="F120" t="n">
-        <v>79793.14999999999</v>
+        <v>1000</v>
       </c>
       <c r="G120" t="n">
-        <v>79793.14999999999</v>
+        <v>11938243</v>
+      </c>
+      <c r="H120" t="n">
+        <v>11938.24</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Sigma Aldrich Co Llc</t>
+          <t>Sinobright Pharmaceutical Indusrtries Ltd</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>202501</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Nos</t>
+          <t>202504</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E121" t="n">
-        <v>28</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F121" t="n">
-        <v>193121.85</v>
+        <v>6000</v>
       </c>
       <c r="G121" t="n">
-        <v>6897.21</v>
+        <v>67969350</v>
+      </c>
+      <c r="H121" t="n">
+        <v>11328.23</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Sigma Aldrich International Gmbh</t>
+          <t>Sinobright Pharmaceutical Indusrtries Ltd</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>202501</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Nos</t>
+          <t>202505</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E122" t="n">
-        <v>2</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
       </c>
       <c r="F122" t="n">
-        <v>22977.63</v>
+        <v>9975</v>
       </c>
       <c r="G122" t="n">
-        <v>11488.82</v>
+        <v>119579900</v>
+      </c>
+      <c r="H122" t="n">
+        <v>11987.96</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Sigma Aldrich International Gmbh</t>
+          <t>Sinobright Pharmaceutical Indusrtries Ltd</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>202502</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Nos</t>
+          <t>202505</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E123" t="n">
-        <v>2</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F123" t="n">
-        <v>28077.96</v>
+        <v>1000</v>
       </c>
       <c r="G123" t="n">
-        <v>14038.98</v>
+        <v>11845894</v>
+      </c>
+      <c r="H123" t="n">
+        <v>11845.89</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Sigma Aldrich International Gmbh</t>
+          <t>Sinobright Pharmaceutical Indusrtries Ltd</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>202504</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Nos</t>
+          <t>202506</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E124" t="n">
-        <v>1</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
       </c>
       <c r="F124" t="n">
-        <v>9306.76</v>
+        <v>16000</v>
       </c>
       <c r="G124" t="n">
-        <v>9306.76</v>
+        <v>193131502</v>
+      </c>
+      <c r="H124" t="n">
+        <v>12070.72</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Sigma Aldrich International Gmbh</t>
+          <t>Sinobright Pharmaceutical Indusrtries Ltd</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>202505</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Nos</t>
+          <t>202506</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E125" t="n">
-        <v>43</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F125" t="n">
-        <v>332755.85</v>
+        <v>750</v>
       </c>
       <c r="G125" t="n">
-        <v>7738.51</v>
+        <v>8845200</v>
+      </c>
+      <c r="H125" t="n">
+        <v>11793.6</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Sigma Aldrich International Gmbh</t>
+          <t>Sinobright Pharmaceutical Indusrtries Ltd</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>202507</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Nos</t>
+          <t>202511</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E126" t="n">
-        <v>6</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
       </c>
       <c r="F126" t="n">
-        <v>171720.88</v>
+        <v>2000</v>
       </c>
       <c r="G126" t="n">
-        <v>28620.15</v>
+        <v>25069812</v>
+      </c>
+      <c r="H126" t="n">
+        <v>12534.91</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Sigma Aldrich International Gmbh</t>
+          <t>Sinobright Pharmaceutical Indusrtries Ltd</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>202508</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Nos</t>
+          <t>202511</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E127" t="n">
-        <v>1</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F127" t="n">
-        <v>10758.52</v>
+        <v>1500</v>
       </c>
       <c r="G127" t="n">
-        <v>10758.52</v>
+        <v>18155875</v>
+      </c>
+      <c r="H127" t="n">
+        <v>12103.92</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Sigma Aldrich International Gmbh</t>
+          <t>Sinobright Pharmaceutical Industrie</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>202510</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Nos</t>
+          <t>202501</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E128" t="n">
-        <v>4</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
       </c>
       <c r="F128" t="n">
-        <v>29607.36</v>
+        <v>6000</v>
       </c>
       <c r="G128" t="n">
-        <v>7401.84</v>
+        <v>73580958</v>
+      </c>
+      <c r="H128" t="n">
+        <v>12263.49</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Sigma Aldrich International Gmbh</t>
+          <t>Sinobright Pharmaceutical Industrie Ltd</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>202601</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Nos</t>
+          <t>202507</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E129" t="n">
-        <v>3</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
       </c>
       <c r="F129" t="n">
-        <v>41459.94</v>
+        <v>11200</v>
       </c>
       <c r="G129" t="n">
-        <v>13819.98</v>
+        <v>133317780</v>
+      </c>
+      <c r="H129" t="n">
+        <v>11903.37</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Sigma Aldrich International Gmbh</t>
+          <t>Sinobright Pharmaceutical Industrie Ltd</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>202602</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Nos</t>
+          <t>202507</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E130" t="n">
-        <v>4</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F130" t="n">
-        <v>69196.84</v>
+        <v>3125</v>
       </c>
       <c r="G130" t="n">
-        <v>17299.21</v>
+        <v>44891876</v>
+      </c>
+      <c r="H130" t="n">
+        <v>14365.4</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Sinobright Pharmaceutical Indusrtries Ltd</t>
+          <t>Sinobright Pharmaceutical Industrie Ltd</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>202503</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202508</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
           <t>IP</t>
         </is>
       </c>
-      <c r="E131" t="n">
-        <v>800</v>
-      </c>
       <c r="F131" t="n">
-        <v>27048938</v>
+        <v>1441.04</v>
       </c>
       <c r="G131" t="n">
-        <v>33811.17</v>
+        <v>17136271.25</v>
+      </c>
+      <c r="H131" t="n">
+        <v>11891.6</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Sinobright Pharmaceutical Indusrtries Ltd</t>
+          <t>Sinobright Pharmaceutical Industrieltd</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>202503</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202508</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E132" t="n">
-        <v>3750</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
       </c>
       <c r="F132" t="n">
-        <v>55890774</v>
+        <v>3000</v>
       </c>
       <c r="G132" t="n">
-        <v>14904.21</v>
+        <v>36414600</v>
+      </c>
+      <c r="H132" t="n">
+        <v>12138.2</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Sinobright Pharmaceutical Indusrtries Ltd</t>
+          <t>Sinobright Pharmaceutical Industries</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>202504</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202509</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
           <t>IP</t>
         </is>
       </c>
-      <c r="E133" t="n">
-        <v>2000</v>
-      </c>
       <c r="F133" t="n">
-        <v>11938243</v>
+        <v>10000</v>
       </c>
       <c r="G133" t="n">
-        <v>5969.12</v>
+        <v>124390000</v>
+      </c>
+      <c r="H133" t="n">
+        <v>12439</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Sinobright Pharmaceutical Indusrtries Ltd</t>
+          <t>Sinobright Pharmaceutical Industries</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>202504</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202509</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E134" t="n">
-        <v>11685.42</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F134" t="n">
-        <v>68065094.96000001</v>
+        <v>2500</v>
       </c>
       <c r="G134" t="n">
-        <v>5824.79</v>
+        <v>30927500</v>
+      </c>
+      <c r="H134" t="n">
+        <v>12371</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Sinobright Pharmaceutical Indusrtries Ltd</t>
+          <t>Sinobright Pharmaceutical Industries Ltd</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>202505</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202501</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
           <t>IP</t>
         </is>
       </c>
-      <c r="E135" t="n">
-        <v>26321</v>
-      </c>
       <c r="F135" t="n">
-        <v>119875820</v>
+        <v>7975</v>
       </c>
       <c r="G135" t="n">
-        <v>4554.38</v>
+        <v>95191867</v>
+      </c>
+      <c r="H135" t="n">
+        <v>11936.28</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Sinobright Pharmaceutical Indusrtries Ltd</t>
+          <t>Sinobright Pharmaceutical Industries Ltd</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>202505</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202501</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E136" t="n">
-        <v>550</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F136" t="n">
-        <v>11845894</v>
+        <v>1626.72</v>
       </c>
       <c r="G136" t="n">
-        <v>21537.99</v>
+        <v>21714904.5</v>
+      </c>
+      <c r="H136" t="n">
+        <v>13348.89</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Sinobright Pharmaceutical Indusrtries Ltd</t>
+          <t>Sinobright Pharmaceutical Industries Ltd</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>202506</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202505</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>IP</t>
-        </is>
-      </c>
-      <c r="E137" t="n">
-        <v>12981.94</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F137" t="n">
-        <v>193131502</v>
+        <v>500</v>
       </c>
       <c r="G137" t="n">
-        <v>14876.94</v>
+        <v>5983200</v>
+      </c>
+      <c r="H137" t="n">
+        <v>11966.4</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Sinobright Pharmaceutical Indusrtries Ltd</t>
+          <t>Sinobright Pharmaceutical Industries Ltd</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>202506</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202509</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E138" t="n">
-        <v>4562</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
       </c>
       <c r="F138" t="n">
-        <v>32026872</v>
+        <v>4550</v>
       </c>
       <c r="G138" t="n">
-        <v>7020.36</v>
+        <v>56105450</v>
+      </c>
+      <c r="H138" t="n">
+        <v>12330.87</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Sinobright Pharmaceutical Indusrtries Ltd</t>
+          <t>Sinobright Pharmaceutical Industries Ltd</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>202511</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202509</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>IP</t>
-        </is>
-      </c>
-      <c r="E139" t="n">
-        <v>5000</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F139" t="n">
-        <v>25069812</v>
+        <v>3950</v>
       </c>
       <c r="G139" t="n">
-        <v>5013.96</v>
+        <v>57147102</v>
+      </c>
+      <c r="H139" t="n">
+        <v>14467.62</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Sinobright Pharmaceutical Indusrtries Ltd</t>
+          <t>Sinobright Pharmaceutical Industries Ltd</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>202511</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202510</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E140" t="n">
-        <v>10175</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F140" t="n">
-        <v>18155875</v>
+        <v>2050</v>
       </c>
       <c r="G140" t="n">
-        <v>1784.36</v>
+        <v>258875</v>
+      </c>
+      <c r="H140" t="n">
+        <v>126.28</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Sinobright Pharmaceutical Industrie</t>
+          <t>Sinobright Pharmaceutical Industries Ltd</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>202501</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202512</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
           <t>IP</t>
         </is>
       </c>
-      <c r="E141" t="n">
-        <v>13395</v>
-      </c>
       <c r="F141" t="n">
-        <v>73580958</v>
+        <v>12000</v>
       </c>
       <c r="G141" t="n">
-        <v>5493.17</v>
+        <v>152150710</v>
+      </c>
+      <c r="H141" t="n">
+        <v>12679.23</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Sinobright Pharmaceutical Industrie Ltd</t>
+          <t>Sinobright Pharmaceutical Industries Ltd</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>202507</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202512</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>IP</t>
-        </is>
-      </c>
-      <c r="E142" t="n">
-        <v>1000</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F142" t="n">
-        <v>17853830</v>
+        <v>20175</v>
       </c>
       <c r="G142" t="n">
-        <v>17853.83</v>
+        <v>235174414</v>
+      </c>
+      <c r="H142" t="n">
+        <v>11656.72</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Sinobright Pharmaceutical Industrie Ltd</t>
+          <t>Sinobright Pharmaceutical Industries Ltd</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>202508</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202601</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
           <t>IP</t>
         </is>
       </c>
-      <c r="E143" t="n">
-        <v>29741</v>
-      </c>
       <c r="F143" t="n">
-        <v>23783199.96</v>
+        <v>14000</v>
       </c>
       <c r="G143" t="n">
-        <v>799.6799999999999</v>
+        <v>179464800</v>
+      </c>
+      <c r="H143" t="n">
+        <v>12818.91</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Sinobright Pharmaceutical Industrieltd</t>
+          <t>Sinobright Pharmaceutical Industries Ltd</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>202508</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202601</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>IP</t>
-        </is>
-      </c>
-      <c r="E144" t="n">
-        <v>2700</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F144" t="n">
-        <v>36414600</v>
+        <v>15895</v>
       </c>
       <c r="G144" t="n">
-        <v>13486.89</v>
+        <v>183127439</v>
+      </c>
+      <c r="H144" t="n">
+        <v>11521.07</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Sinobright Pharmaceutical Industries</t>
+          <t>Sinobright Pharmaceutical Industries Ltd</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>202509</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202602</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>IP</t>
-        </is>
-      </c>
-      <c r="E145" t="n">
-        <v>2000</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F145" t="n">
-        <v>124390000</v>
+        <v>9700</v>
       </c>
       <c r="G145" t="n">
-        <v>62195</v>
+        <v>109504648</v>
+      </c>
+      <c r="H145" t="n">
+        <v>11289.14</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Sinobright Pharmaceutical Industries</t>
+          <t>To The Order</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>202509</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202510</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E146" t="n">
-        <v>2875</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F146" t="n">
-        <v>30927500</v>
+        <v>9400</v>
       </c>
       <c r="G146" t="n">
-        <v>10757.39</v>
+        <v>1181126.06</v>
+      </c>
+      <c r="H146" t="n">
+        <v>125.65</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Sinobright Pharmaceutical Industries Ltd</t>
+          <t>Zhejiang Guobang Pharmaceutical Co</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
           <t>202501</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>IP</t>
-        </is>
-      </c>
-      <c r="E147" t="n">
-        <v>17775</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F147" t="n">
-        <v>95191867</v>
+        <v>210</v>
       </c>
       <c r="G147" t="n">
-        <v>5355.38</v>
+        <v>2579031</v>
+      </c>
+      <c r="H147" t="n">
+        <v>12281.1</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Sinobright Pharmaceutical Industries Ltd</t>
+          <t>Zhejiang Guobang Pharmaceutical Co Ltd</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
           <t>202501</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E148" t="n">
-        <v>37381</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
       </c>
       <c r="F148" t="n">
-        <v>22645883.38</v>
+        <v>250</v>
       </c>
       <c r="G148" t="n">
-        <v>605.8099999999999</v>
+        <v>3031000</v>
+      </c>
+      <c r="H148" t="n">
+        <v>12124</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Sinobright Pharmaceutical Industries Ltd</t>
+          <t>Zhejiang Guobang Pharmaceutical Co Ltd</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>202505</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202501</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E149" t="n">
-        <v>500</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F149" t="n">
-        <v>5983200</v>
+        <v>5250</v>
       </c>
       <c r="G149" t="n">
-        <v>11966.4</v>
+        <v>63944882.5</v>
+      </c>
+      <c r="H149" t="n">
+        <v>12179.98</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Sinobright Pharmaceutical Industries Ltd</t>
+          <t>Zhejiang Guobang Pharmaceutical Co Ltd</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>202509</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202502</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
           <t>IP</t>
         </is>
       </c>
-      <c r="E150" t="n">
-        <v>7700</v>
-      </c>
       <c r="F150" t="n">
-        <v>56105450</v>
+        <v>250</v>
       </c>
       <c r="G150" t="n">
-        <v>7286.42</v>
+        <v>3094000</v>
+      </c>
+      <c r="H150" t="n">
+        <v>12376</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Sinobright Pharmaceutical Industries Ltd</t>
+          <t>Zhejiang Guobang Pharmaceutical Co Ltd</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>202509</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202502</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E151" t="n">
-        <v>6150</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F151" t="n">
-        <v>57147102</v>
+        <v>19000</v>
       </c>
       <c r="G151" t="n">
-        <v>9292.209999999999</v>
+        <v>237592946</v>
+      </c>
+      <c r="H151" t="n">
+        <v>12504.89</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Sinobright Pharmaceutical Industries Ltd</t>
+          <t>Zhejiang Guobang Pharmaceutical Co Ltd</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>202510</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202503</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E152" t="n">
-        <v>4725</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F152" t="n">
-        <v>258875</v>
+        <v>8000</v>
       </c>
       <c r="G152" t="n">
-        <v>54.79</v>
+        <v>99623812.5</v>
+      </c>
+      <c r="H152" t="n">
+        <v>12452.98</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Sinobright Pharmaceutical Industries Ltd</t>
+          <t>Zhejiang Guobang Pharmaceutical Co Ltd</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>202512</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202504</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
           <t>IP</t>
         </is>
       </c>
-      <c r="E153" t="n">
-        <v>7914.86</v>
-      </c>
       <c r="F153" t="n">
-        <v>152150710</v>
+        <v>250</v>
       </c>
       <c r="G153" t="n">
-        <v>19223.42</v>
+        <v>3031000</v>
+      </c>
+      <c r="H153" t="n">
+        <v>12124</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Sinobright Pharmaceutical Industries Ltd</t>
+          <t>Zhejiang Guobang Pharmaceutical Co Ltd</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>202512</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202504</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E154" t="n">
-        <v>8761.280000000001</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F154" t="n">
-        <v>235322776.5</v>
+        <v>16000</v>
       </c>
       <c r="G154" t="n">
-        <v>26859.41</v>
+        <v>191882000</v>
+      </c>
+      <c r="H154" t="n">
+        <v>11992.62</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Sinobright Pharmaceutical Industries Ltd</t>
+          <t>Zhejiang Guobang Pharmaceutical Co Ltd</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>202601</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202505</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
           <t>IP</t>
         </is>
       </c>
-      <c r="E155" t="n">
-        <v>4800</v>
-      </c>
       <c r="F155" t="n">
-        <v>179464800</v>
+        <v>250</v>
       </c>
       <c r="G155" t="n">
-        <v>37388.5</v>
+        <v>2994250</v>
+      </c>
+      <c r="H155" t="n">
+        <v>11977</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Sinobright Pharmaceutical Industries Ltd</t>
+          <t>Zhejiang Guobang Pharmaceutical Co Ltd</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>202601</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202505</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E156" t="n">
-        <v>17595</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F156" t="n">
-        <v>184779999</v>
+        <v>7370.3</v>
       </c>
       <c r="G156" t="n">
-        <v>10501.85</v>
+        <v>86684425</v>
+      </c>
+      <c r="H156" t="n">
+        <v>11761.32</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Sinobright Pharmaceutical Industries Ltd</t>
+          <t>Zhejiang Guobang Pharmaceutical Co Ltd</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>202602</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202506</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E157" t="n">
-        <v>13950</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F157" t="n">
-        <v>109574530.75</v>
+        <v>4000</v>
       </c>
       <c r="G157" t="n">
-        <v>7854.81</v>
+        <v>48863820</v>
+      </c>
+      <c r="H157" t="n">
+        <v>12215.95</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Somex Pharma</t>
+          <t>Zhejiang Guobang Pharmaceutical Co Ltd</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>202504</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202507</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E158" t="n">
-        <v>4539.64</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>EP</t>
+        </is>
       </c>
       <c r="F158" t="n">
-        <v>2353788</v>
+        <v>3000</v>
       </c>
       <c r="G158" t="n">
-        <v>518.5</v>
+        <v>36204000</v>
+      </c>
+      <c r="H158" t="n">
+        <v>12068</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Taj Shuraim General Trading Llc</t>
+          <t>Zhejiang Guobang Pharmaceutical Co Ltd</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>202503</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202507</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E159" t="n">
-        <v>2146.28</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F159" t="n">
-        <v>15804000</v>
+        <v>22825</v>
       </c>
       <c r="G159" t="n">
-        <v>7363.44</v>
+        <v>275955029.25</v>
+      </c>
+      <c r="H159" t="n">
+        <v>12090.03</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Tapi Croatia Industries Ltd</t>
+          <t>Zhejiang Guobang Pharmaceutical Co Ltd</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>202507</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Gms</t>
+          <t>202508</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E160" t="n">
-        <v>0.25</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F160" t="n">
-        <v>789.88</v>
+        <v>4500</v>
       </c>
       <c r="G160" t="n">
-        <v>3159.52</v>
+        <v>55328764</v>
+      </c>
+      <c r="H160" t="n">
+        <v>12295.28</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Tapi Nl B V</t>
+          <t>Zhejiang Guobang Pharmaceutical Co Ltd</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
           <t>202509</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E161" t="n">
-        <v>1700</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F161" t="n">
-        <v>6219500</v>
+        <v>12125</v>
       </c>
       <c r="G161" t="n">
-        <v>3658.53</v>
+        <v>150816618</v>
+      </c>
+      <c r="H161" t="n">
+        <v>12438.48</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Tapi Nl Bv</t>
+          <t>Zhejiang Guobang Pharmaceutical Co Ltd</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>202504</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202510</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E162" t="n">
-        <v>5375</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
       </c>
       <c r="F162" t="n">
-        <v>3788750</v>
+        <v>210</v>
       </c>
       <c r="G162" t="n">
-        <v>704.88</v>
+        <v>31920</v>
+      </c>
+      <c r="H162" t="n">
+        <v>152</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Tapi Nl Bv</t>
+          <t>Zhejiang Guobang Pharmaceutical Co Ltd</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>202506</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202510</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E163" t="n">
-        <v>4050</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F163" t="n">
-        <v>25951500</v>
+        <v>7000</v>
       </c>
       <c r="G163" t="n">
-        <v>6407.78</v>
+        <v>989198.1</v>
+      </c>
+      <c r="H163" t="n">
+        <v>141.31</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Tapi Nl Bv</t>
+          <t>Zhejiang Guobang Pharmaceutical Co Ltd</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>202601</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202511</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E164" t="n">
-        <v>1260.48</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F164" t="n">
-        <v>19068000</v>
+        <v>1000</v>
       </c>
       <c r="G164" t="n">
-        <v>15127.57</v>
+        <v>12595400</v>
+      </c>
+      <c r="H164" t="n">
+        <v>12595.4</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Tawazon General Trading Llc</t>
+          <t>Zhejiang Guobang Pharmaceutical Co Ltd</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>202505</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202512</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E165" t="n">
-        <v>229.5</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F165" t="n">
-        <v>648000</v>
+        <v>10850</v>
       </c>
       <c r="G165" t="n">
-        <v>2823.53</v>
+        <v>140936336</v>
+      </c>
+      <c r="H165" t="n">
+        <v>12989.52</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>To The Order</t>
+          <t>Zhejiang Guobang Pharmaceutical Co Ltd</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>202510</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202601</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E166" t="n">
-        <v>500</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F166" t="n">
-        <v>1181126.06</v>
+        <v>12613</v>
       </c>
       <c r="G166" t="n">
-        <v>2362.25</v>
+        <v>163559403</v>
+      </c>
+      <c r="H166" t="n">
+        <v>12967.53</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Tokyo Chemical Industry Co Ltd</t>
+          <t>Zhejiang Guobang Pharmaceutical Co Ltd</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>202501</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Nos</t>
+          <t>202602</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E167" t="n">
-        <v>4</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F167" t="n">
-        <v>3871.99</v>
+        <v>8300</v>
       </c>
       <c r="G167" t="n">
-        <v>968</v>
+        <v>108255013</v>
+      </c>
+      <c r="H167" t="n">
+        <v>13042.77</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Tokyo Chemical Industry Co Ltd</t>
+          <t>Zhejiang Guobang Pharmaceuticals Co Ltd</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>202503</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Nos</t>
+          <t>202509</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E168" t="n">
-        <v>1</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F168" t="n">
-        <v>975.78</v>
+        <v>1000</v>
       </c>
       <c r="G168" t="n">
-        <v>975.78</v>
+        <v>12460000</v>
+      </c>
+      <c r="H168" t="n">
+        <v>12460</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Tokyo Chemical Industry Co Ltd</t>
+          <t>Zhejiang Guobang Pharmaceuticals Co Ltd</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>202509</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Nos</t>
+          <t>202510</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E169" t="n">
-        <v>1</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F169" t="n">
-        <v>976.89</v>
+        <v>1000</v>
       </c>
       <c r="G169" t="n">
-        <v>976.89</v>
+        <v>140000</v>
+      </c>
+      <c r="H169" t="n">
+        <v>140</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Tokyo Chemical Industry Co Ltd</t>
+          <t>Zhejiang Guobang Pharmeceutical Co Ltd</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
           <t>202512</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Nos</t>
-        </is>
-      </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E170" t="n">
-        <v>1</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F170" t="n">
-        <v>994.67</v>
+        <v>600</v>
       </c>
       <c r="G170" t="n">
-        <v>994.67</v>
+        <v>7625400</v>
+      </c>
+      <c r="H170" t="n">
+        <v>12709</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Tokyo Chemical Industry Co Ltd</t>
+          <t>Zhejiang Guobang Pharmeceutical Co Ltd</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
           <t>202601</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>Nos</t>
-        </is>
-      </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E171" t="n">
-        <v>7</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F171" t="n">
-        <v>5455.17</v>
+        <v>443</v>
       </c>
       <c r="G171" t="n">
-        <v>779.3099999999999</v>
+        <v>5711865</v>
+      </c>
+      <c r="H171" t="n">
+        <v>12893.6</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Tokyo Chemical Industry Co Ltd</t>
+          <t>Zhejiang Guobang Pharmeceutical Co Ltd</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
           <t>202602</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>Nos</t>
-        </is>
-      </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E172" t="n">
-        <v>1</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F172" t="n">
-        <v>780.59</v>
+        <v>500</v>
       </c>
       <c r="G172" t="n">
-        <v>780.59</v>
+        <v>6485850</v>
+      </c>
+      <c r="H172" t="n">
+        <v>12971.7</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>United States Pharmacopeial Convention</t>
+          <t>Zhejiang Hengdian Apeloa Import And Export Co Ltd</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>202508</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Nos</t>
+          <t>202503</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E173" t="n">
-        <v>1</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F173" t="n">
-        <v>256293.7</v>
+        <v>350</v>
       </c>
       <c r="G173" t="n">
-        <v>256293.7</v>
+        <v>4247145</v>
+      </c>
+      <c r="H173" t="n">
+        <v>12134.7</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>United States Pharmacopeial Convention</t>
+          <t>Zhejiang Hengdian Apeloa Import And Export Co Ltd</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>202510</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Nos</t>
+          <t>202504</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E174" t="n">
-        <v>1</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F174" t="n">
-        <v>889.2</v>
+        <v>500</v>
       </c>
       <c r="G174" t="n">
-        <v>889.2</v>
+        <v>6004800</v>
+      </c>
+      <c r="H174" t="n">
+        <v>12009.6</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Zhejiang Guobang Pharmaceutical Co</t>
+          <t>Zhejiang Hengdian Apeloa Import And Export Co Ltd</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>202501</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202601</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E175" t="n">
-        <v>3150</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F175" t="n">
-        <v>2579031</v>
+        <v>850</v>
       </c>
       <c r="G175" t="n">
-        <v>818.74</v>
+        <v>10542720</v>
+      </c>
+      <c r="H175" t="n">
+        <v>12403.2</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Zhejiang Guobang Pharmaceutical Co Ltd</t>
+          <t>Zhejiang Ueasy Business Service Co Ltd</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>202501</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202504</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>IP</t>
-        </is>
-      </c>
-      <c r="E176" t="n">
-        <v>6000</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F176" t="n">
-        <v>3031000</v>
+        <v>1000</v>
       </c>
       <c r="G176" t="n">
-        <v>505.17</v>
+        <v>10022400</v>
+      </c>
+      <c r="H176" t="n">
+        <v>10022.4</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Zhejiang Guobang Pharmaceutical Co Ltd</t>
+          <t>Zhejiang Ueasy Business Service Co Ltd</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>202501</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202505</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E177" t="n">
-        <v>32662.35</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F177" t="n">
-        <v>64249732.5</v>
+        <v>980</v>
       </c>
       <c r="G177" t="n">
-        <v>1967.09</v>
+        <v>9821952</v>
+      </c>
+      <c r="H177" t="n">
+        <v>10022.4</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Zhejiang Guobang Pharmaceutical Co Ltd</t>
+          <t>Zhejiang Ueasy Business Service Co Ltd</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>202502</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202506</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
           <t>IP</t>
         </is>
       </c>
-      <c r="E178" t="n">
-        <v>1000</v>
-      </c>
       <c r="F178" t="n">
-        <v>3094000</v>
+        <v>4275</v>
       </c>
       <c r="G178" t="n">
-        <v>3094</v>
+        <v>51883124</v>
+      </c>
+      <c r="H178" t="n">
+        <v>12136.4</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Zhejiang Guobang Pharmaceutical Co Ltd</t>
+          <t>Zhejiang Ueasy Business Service Co Ltd</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>202502</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202506</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E179" t="n">
-        <v>2200</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>USP</t>
+        </is>
       </c>
       <c r="F179" t="n">
-        <v>27225700</v>
+        <v>1000</v>
       </c>
       <c r="G179" t="n">
-        <v>12375.32</v>
+        <v>10264260</v>
+      </c>
+      <c r="H179" t="n">
+        <v>10264.26</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Zhejiang Guobang Pharmaceutical Co Ltd</t>
+          <t>Zhejiang Ueasy Business Service Co Ltd</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>202503</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>202507</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E180" t="n">
-        <v>24694.45</v>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
       </c>
       <c r="F180" t="n">
-        <v>107329242.53</v>
+        <v>2350</v>
       </c>
       <c r="G180" t="n">
-        <v>4346.29</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>Zhejiang Guobang Pharmaceutical Co Ltd</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>202504</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>IP</t>
-        </is>
-      </c>
-      <c r="E181" t="n">
-        <v>4682</v>
-      </c>
-      <c r="F181" t="n">
-        <v>3031000</v>
-      </c>
-      <c r="G181" t="n">
-        <v>647.37</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Zhejiang Guobang Pharmaceutical Co Ltd</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>202504</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E182" t="n">
-        <v>16129</v>
-      </c>
-      <c r="F182" t="n">
-        <v>191882000</v>
-      </c>
-      <c r="G182" t="n">
-        <v>11896.71</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>Zhejiang Guobang Pharmaceutical Co Ltd</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>202505</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>IP</t>
-        </is>
-      </c>
-      <c r="E183" t="n">
-        <v>500</v>
-      </c>
-      <c r="F183" t="n">
-        <v>2994250</v>
-      </c>
-      <c r="G183" t="n">
-        <v>5988.5</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>Zhejiang Guobang Pharmaceutical Co Ltd</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>202505</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E184" t="n">
-        <v>10129.68</v>
-      </c>
-      <c r="F184" t="n">
-        <v>87043676.19</v>
-      </c>
-      <c r="G184" t="n">
-        <v>8592.93</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>Zhejiang Guobang Pharmaceutical Co Ltd</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>202506</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E185" t="n">
-        <v>12450</v>
-      </c>
-      <c r="F185" t="n">
-        <v>53772219.94</v>
-      </c>
-      <c r="G185" t="n">
-        <v>4319.05</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>Zhejiang Guobang Pharmaceutical Co Ltd</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>202508</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E186" t="n">
-        <v>5450</v>
-      </c>
-      <c r="F186" t="n">
-        <v>55328764</v>
-      </c>
-      <c r="G186" t="n">
-        <v>10152.07</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>Zhejiang Guobang Pharmaceutical Co Ltd</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>202509</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E187" t="n">
-        <v>24916.36</v>
-      </c>
-      <c r="F187" t="n">
-        <v>158600818</v>
-      </c>
-      <c r="G187" t="n">
-        <v>6365.33</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>Zhejiang Guobang Pharmaceutical Co Ltd</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>202510</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>IP</t>
-        </is>
-      </c>
-      <c r="E188" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F188" t="n">
-        <v>31920</v>
-      </c>
-      <c r="G188" t="n">
-        <v>6.38</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>Zhejiang Guobang Pharmaceutical Co Ltd</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>202510</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E189" t="n">
-        <v>10772.46</v>
-      </c>
-      <c r="F189" t="n">
-        <v>989198.1</v>
-      </c>
-      <c r="G189" t="n">
-        <v>91.83</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>Zhejiang Guobang Pharmaceutical Co Ltd</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>202511</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E190" t="n">
-        <v>16435</v>
-      </c>
-      <c r="F190" t="n">
-        <v>12670490.5</v>
-      </c>
-      <c r="G190" t="n">
-        <v>770.95</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>Zhejiang Guobang Pharmaceutical Co Ltd</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>202512</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>IP</t>
-        </is>
-      </c>
-      <c r="E191" t="n">
-        <v>822.72</v>
-      </c>
-      <c r="F191" t="n">
-        <v>2774000</v>
-      </c>
-      <c r="G191" t="n">
-        <v>3371.74</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>Zhejiang Guobang Pharmaceutical Co Ltd</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>202512</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E192" t="n">
-        <v>17096.65</v>
-      </c>
-      <c r="F192" t="n">
-        <v>140936336</v>
-      </c>
-      <c r="G192" t="n">
-        <v>8243.51</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>Zhejiang Guobang Pharmaceutical Co Ltd</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>202601</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E193" t="n">
-        <v>14547.89</v>
-      </c>
-      <c r="F193" t="n">
-        <v>165346320.44</v>
-      </c>
-      <c r="G193" t="n">
-        <v>11365.66</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>Zhejiang Guobang Pharmaceutical Co Ltd</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>202602</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E194" t="n">
-        <v>10000</v>
-      </c>
-      <c r="F194" t="n">
-        <v>108255013</v>
-      </c>
-      <c r="G194" t="n">
-        <v>10825.5</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>Zhejiang Guobang Pharmaceuticals Co Ltd</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>202509</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E195" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F195" t="n">
-        <v>12460000</v>
-      </c>
-      <c r="G195" t="n">
-        <v>6230</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>Zhejiang Guobang Pharmaceuticals Co Ltd</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>202510</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E196" t="n">
-        <v>4350</v>
-      </c>
-      <c r="F196" t="n">
-        <v>140000</v>
-      </c>
-      <c r="G196" t="n">
-        <v>32.18</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>Zhejiang Guobang Pharmeceutical Co Ltd</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>202512</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E197" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F197" t="n">
-        <v>7625400</v>
-      </c>
-      <c r="G197" t="n">
-        <v>7625.4</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>Zhejiang Guobang Pharmeceutical Co Ltd</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>202601</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E198" t="n">
-        <v>944.48</v>
-      </c>
-      <c r="F198" t="n">
-        <v>7736160.25</v>
-      </c>
-      <c r="G198" t="n">
-        <v>8190.92</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>Zhejiang Guobang Pharmeceutical Co Ltd</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>202602</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E199" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F199" t="n">
-        <v>6485850</v>
-      </c>
-      <c r="G199" t="n">
-        <v>6485.85</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>Zhejiang Hengdian Apeloa Import And Export Co Ltd</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>202503</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E200" t="n">
-        <v>1382.2</v>
-      </c>
-      <c r="F200" t="n">
-        <v>6067350</v>
-      </c>
-      <c r="G200" t="n">
-        <v>4389.63</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>Zhejiang Hengdian Apeloa Import And Export Co Ltd</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>202504</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E201" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F201" t="n">
-        <v>6004800</v>
-      </c>
-      <c r="G201" t="n">
-        <v>3002.4</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>Zhejiang Hengdian Apeloa Import And Export Co Ltd</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>202601</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E202" t="n">
-        <v>709.97</v>
-      </c>
-      <c r="F202" t="n">
-        <v>12403200</v>
-      </c>
-      <c r="G202" t="n">
-        <v>17470.03</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>Zhejiang Ueasy Business Service Co Ltd</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>202504</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E203" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F203" t="n">
-        <v>10022400</v>
-      </c>
-      <c r="G203" t="n">
-        <v>2004.48</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>Zhejiang Ueasy Business Service Co Ltd</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>202505</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E204" t="n">
-        <v>1500</v>
-      </c>
-      <c r="F204" t="n">
-        <v>9821952</v>
-      </c>
-      <c r="G204" t="n">
-        <v>6547.97</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>Zhejiang Ueasy Business Service Co Ltd</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>202506</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>IP</t>
-        </is>
-      </c>
-      <c r="E205" t="n">
-        <v>2719</v>
-      </c>
-      <c r="F205" t="n">
-        <v>51883124</v>
-      </c>
-      <c r="G205" t="n">
-        <v>19081.69</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>Zhejiang Ueasy Business Service Co Ltd</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>202506</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>Kg</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>USP</t>
-        </is>
-      </c>
-      <c r="E206" t="n">
-        <v>1327.75</v>
-      </c>
-      <c r="F206" t="n">
-        <v>10264260</v>
-      </c>
-      <c r="G206" t="n">
-        <v>7730.57</v>
+        <v>28359800</v>
+      </c>
+      <c r="H180" t="n">
+        <v>12068</v>
       </c>
     </row>
   </sheetData>
